--- a/DCS_Missions/DCS_Maps/Syria/Base/Kneeboards/presets.xlsx
+++ b/DCS_Missions/DCS_Maps/Syria/Base/Kneeboards/presets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repo\DCS\DCS_Missions\DCS_Maps\Syria\Base\Kneeboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90A79DD-62B2-4075-B152-B47B8A08C3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D735730-C18A-4C6D-9F3D-7C281353C080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11280" yWindow="2835" windowWidth="43200" windowHeight="17145" xr2:uid="{0FCC770A-A480-4475-A2DE-100B627674D7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{0FCC770A-A480-4475-A2DE-100B627674D7}"/>
   </bookViews>
   <sheets>
     <sheet name="F-15E" sheetId="18" r:id="rId1"/>
@@ -1185,7 +1185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1732,117 +1732,59 @@
     <xf numFmtId="0" fontId="1" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1913,9 +1855,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1953,7 +1895,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2059,7 +2001,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2201,7 +2143,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2222,24 +2164,24 @@
   <sheetData>
     <row r="2" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>248</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -2277,10 +2219,10 @@
       <c r="G6" s="88">
         <v>1</v>
       </c>
-      <c r="H6" s="207" t="s">
+      <c r="H6" s="196" t="s">
         <v>91</v>
       </c>
-      <c r="I6" s="208" t="s">
+      <c r="I6" s="197" t="s">
         <v>92</v>
       </c>
       <c r="J6" s="88">
@@ -2806,10 +2748,10 @@
       <c r="G25" s="186">
         <v>20</v>
       </c>
-      <c r="H25" s="209" t="s">
+      <c r="H25" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="I25" s="210" t="s">
+      <c r="I25" s="199" t="s">
         <v>132</v>
       </c>
       <c r="J25" s="165">
@@ -2843,13 +2785,13 @@
       <c r="E28" s="150"/>
       <c r="F28" s="150"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="196" t="s">
+      <c r="H28" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="197"/>
+      <c r="I28" s="207"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="211"/>
-      <c r="L28" s="211"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
     </row>
     <row r="29" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D29" s="149" t="s">
@@ -2888,11 +2830,9 @@
       <c r="L31" s="86"/>
     </row>
     <row r="32" spans="4:14" x14ac:dyDescent="0.25">
-      <c r="D32" s="212"/>
-      <c r="E32" s="213"/>
-      <c r="F32" s="214"/>
-      <c r="G32" s="213"/>
-      <c r="H32" s="215"/>
+      <c r="D32" s="50"/>
+      <c r="F32" s="28"/>
+      <c r="H32" s="86"/>
       <c r="I32" s="87"/>
       <c r="J32" s="2"/>
       <c r="K32" s="86"/>
@@ -2955,24 +2895,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="57" t="s">
@@ -3283,10 +3223,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -3356,24 +3296,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -3635,10 +3575,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -3708,24 +3648,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -4080,10 +4020,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -4157,37 +4097,37 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>224</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="204" t="s">
+      <c r="D5" s="210" t="s">
         <v>225</v>
       </c>
-      <c r="E5" s="205"/>
+      <c r="E5" s="211"/>
       <c r="F5" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="G5" s="204" t="s">
+      <c r="G5" s="210" t="s">
         <v>226</v>
       </c>
-      <c r="H5" s="205"/>
+      <c r="H5" s="211"/>
       <c r="I5" s="43" t="s">
         <v>227</v>
       </c>
@@ -4308,7 +4248,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="206"/>
+      <c r="J16" s="209"/>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D17" s="106"/>
@@ -4317,7 +4257,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="206"/>
+      <c r="J17" s="209"/>
     </row>
     <row r="18" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D18" s="123"/>
@@ -4326,7 +4266,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="206"/>
+      <c r="J18" s="209"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="123"/>
@@ -4335,7 +4275,7 @@
       <c r="G19" s="106"/>
       <c r="H19" s="107"/>
       <c r="I19" s="108"/>
-      <c r="J19" s="206"/>
+      <c r="J19" s="209"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="93"/>
@@ -4486,10 +4426,10 @@
       <c r="E37" s="132"/>
       <c r="F37" s="132"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="196" t="s">
+      <c r="H37" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="197"/>
+      <c r="I37" s="207"/>
     </row>
     <row r="38" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D38" s="133" t="s">
@@ -4593,30 +4533,30 @@
   <sheetData>
     <row r="2" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202"/>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202"/>
-      <c r="L3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="204"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="201"/>
     </row>
     <row r="4" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="203"/>
-      <c r="J4" s="203"/>
-      <c r="K4" s="203"/>
-      <c r="L4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="205"/>
+      <c r="K4" s="205"/>
+      <c r="L4" s="203"/>
     </row>
     <row r="5" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -5257,7 +5197,7 @@
       <c r="L27" s="130" t="s">
         <v>145</v>
       </c>
-      <c r="M27" s="206"/>
+      <c r="M27" s="209"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" s="128">
@@ -5287,7 +5227,7 @@
       <c r="L28" s="130" t="s">
         <v>146</v>
       </c>
-      <c r="M28" s="206"/>
+      <c r="M28" s="209"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" s="128">
@@ -5317,7 +5257,7 @@
       <c r="L29" s="130" t="s">
         <v>147</v>
       </c>
-      <c r="M29" s="206"/>
+      <c r="M29" s="209"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D30" s="128">
@@ -5347,7 +5287,7 @@
       <c r="L30" s="130" t="s">
         <v>148</v>
       </c>
-      <c r="M30" s="206"/>
+      <c r="M30" s="209"/>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D31" s="128">
@@ -5478,10 +5418,10 @@
       <c r="H39" s="132"/>
       <c r="I39" s="132"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="196" t="s">
+      <c r="K39" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="197"/>
+      <c r="L39" s="207"/>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D40" s="133" t="s">
@@ -5596,24 +5536,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="155" t="s">
@@ -5750,7 +5690,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="206"/>
+      <c r="J16" s="209"/>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D17" s="89"/>
@@ -5759,7 +5699,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="206"/>
+      <c r="J17" s="209"/>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D18" s="89"/>
@@ -5768,7 +5708,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="206"/>
+      <c r="J18" s="209"/>
     </row>
     <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D19" s="89"/>
@@ -5777,7 +5717,7 @@
       <c r="G19" s="89"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="206"/>
+      <c r="J19" s="209"/>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D20" s="89"/>
@@ -5855,10 +5795,10 @@
       <c r="E29" s="150"/>
       <c r="F29" s="150"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D30" s="149" t="s">
@@ -5937,24 +5877,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>179</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="155" t="s">
@@ -6119,7 +6059,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="206"/>
+      <c r="J16" s="209"/>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D17" s="156">
@@ -6134,7 +6074,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="206"/>
+      <c r="J17" s="209"/>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -6149,7 +6089,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="206"/>
+      <c r="J18" s="209"/>
     </row>
     <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -6164,7 +6104,7 @@
       <c r="G19" s="89"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="206"/>
+      <c r="J19" s="209"/>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D20" s="128">
@@ -6276,10 +6216,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D30" s="50"/>
@@ -6356,24 +6296,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -6610,7 +6550,7 @@
       <c r="I16" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="206"/>
+      <c r="J16" s="209"/>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -6631,7 +6571,7 @@
       <c r="I17" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="J17" s="206"/>
+      <c r="J17" s="209"/>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -6652,7 +6592,7 @@
       <c r="I18" s="91" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="206"/>
+      <c r="J18" s="209"/>
     </row>
     <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -6671,7 +6611,7 @@
         <v>171</v>
       </c>
       <c r="I19" s="91"/>
-      <c r="J19" s="206"/>
+      <c r="J19" s="209"/>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D20" s="115">
@@ -6809,10 +6749,10 @@
       <c r="E29" s="150"/>
       <c r="F29" s="150"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D30" s="149" t="s">
@@ -6897,24 +6837,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -7152,7 +7092,7 @@
       <c r="I16" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="206"/>
+      <c r="J16" s="209"/>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -7173,7 +7113,7 @@
       <c r="I17" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="J17" s="206"/>
+      <c r="J17" s="209"/>
     </row>
     <row r="18" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -7194,7 +7134,7 @@
       <c r="I18" s="91" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="206"/>
+      <c r="J18" s="209"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -7215,7 +7155,7 @@
       <c r="I19" s="108" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="206"/>
+      <c r="J19" s="209"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="93">
@@ -7366,10 +7306,10 @@
       <c r="E29" s="132"/>
       <c r="F29" s="132"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D30" s="133" t="s">
@@ -7468,37 +7408,37 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>231</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="204" t="s">
+      <c r="D5" s="210" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="205"/>
+      <c r="E5" s="211"/>
       <c r="F5" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="204" t="s">
+      <c r="G5" s="210" t="s">
         <v>221</v>
       </c>
-      <c r="H5" s="205"/>
+      <c r="H5" s="211"/>
       <c r="I5" s="43" t="s">
         <v>223</v>
       </c>
@@ -7723,7 +7663,7 @@
       <c r="I16" s="92" t="s">
         <v>155</v>
       </c>
-      <c r="J16" s="206"/>
+      <c r="J16" s="209"/>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -7744,7 +7684,7 @@
       <c r="I17" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="J17" s="206"/>
+      <c r="J17" s="209"/>
     </row>
     <row r="18" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -7765,7 +7705,7 @@
       <c r="I18" s="91" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="206"/>
+      <c r="J18" s="209"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -7786,7 +7726,7 @@
       <c r="I19" s="108" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="206"/>
+      <c r="J19" s="209"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="93">
@@ -8065,10 +8005,10 @@
       <c r="E37" s="132"/>
       <c r="F37" s="132"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="196" t="s">
+      <c r="H37" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="197"/>
+      <c r="I37" s="207"/>
     </row>
     <row r="38" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D38" s="133" t="s">
@@ -8195,24 +8135,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="200" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="199"/>
-      <c r="F3" s="198" t="s">
+      <c r="E3" s="201"/>
+      <c r="F3" s="200" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="199"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="201"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="201"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="203"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -8560,10 +8500,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="196" t="s">
+      <c r="H29" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="197"/>
+      <c r="I29" s="207"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
